--- a/NF_Guidelines_Curated.xlsx
+++ b/NF_Guidelines_Curated.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classified Papers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary Counts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Year" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Classified Papers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary Counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="By Year" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/NF_Guidelines_Curated.xlsx
+++ b/NF_Guidelines_Curated.xlsx
@@ -1949,16 +1949,8 @@
           <t>Consensus statement</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Optic pathway glioma; Low grade glioma</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -3884,16 +3876,8 @@
           <t>Consensus statement</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Optic pathway glioma; Low grade glioma</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -4730,69 +4714,29 @@
           <t>abstract_only</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Clinical practice guideline</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>NF2-SWN</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Hearing loss / Deafness; Facial weakness</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Systematic review &amp; meta-analysis</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Weak/Conditional</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>CNS (Congress of Neurological Surgeons)</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>All recommendations are Level 3 (lowest evidence tier in CNS grading), covering emerging pharmacological therapies (bevacizumab, lapatinib, erlotinib, everolimus, aspirin), perioperative interventions (nimodipine, hydroxyethyl starch, gentamicin ablation), preoperative vestibular rehabilitation, and endoscopic surgical assistance for vestibular schwannomas. NF2 is specifically addressed in drug therapy sections; general VS population addressed for surgical sections. Part of a larger multi-chapter CNS guideline series on vestibular schwannoma management.</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4820,69 +4764,29 @@
           <t>abstract_only</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Clinical practice guideline</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>NF2-SWN</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Hearing loss / Deafness; Facial weakness</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Systematic review &amp; meta-analysis</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Weak/Conditional</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Congress of Neurological Surgeons (CNS)</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Systematic review and evidence-based guideline focused on imaging (MRI) for vestibular schwannoma diagnosis, surveillance, and post-surgical follow-up. Includes a specific section on NF2 patients. All recommendations are Level 2 or Level 3 (weak/conditional), reflecting limited high-quality evidence. Part of a larger CNS vestibular schwannoma guideline series.</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5320,17 +5224,9 @@
           <t>Consensus statement</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>NF2-SWN</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
@@ -5600,65 +5496,29 @@
           <t>PMC XML</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Consensus statement</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Cutaneous neurofibroma; Plexiform neurofibroma; MPNST / triton tumor</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Consensus conference / expert panel</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Expert opinion only</t>
-        </is>
-      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>This is a research-priority consensus statement focused on the biology of cutaneous neurofibromas (cNF) in NF1, not a clinical care guideline. It provides consensus recommendations for future research directions (cell of origin, tumor microenvironment, genotype-phenotype correlations, sex hormones, and in vitro/in vivo models) rather than clinical management or treatment recommendations. No formal evidence grading methodology was applied.</t>
-        </is>
-      </c>
+      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5686,69 +5546,29 @@
           <t>abstract_only</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Expert recommendation</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Cutaneous neurofibroma</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N88" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Consensus conference / expert panel</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>Expert opinion only</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>CTF</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Product of CTF's Therapies Development Working Group; outlines consensus-based recommendations and key considerations for drug discovery and development for cutaneous neurofibromas. Clinical trial data reviewed but limited; recommendations are largely expert-driven. Part of a broader NF1 guidelines initiative.</t>
-        </is>
-      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5776,69 +5596,29 @@
           <t>PMC XML</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Consensus statement</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Cutaneous neurofibroma</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O89" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P89" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Consensus conference / expert panel</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Expert opinion only</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>CTF (Children's Tumor Foundation) / REiNS</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>This is a consensus statement from the Clinical Trial Design and Development subgroup focused on cNF clinical trial design, outcome measures, PROs, and regulatory considerations. Part of the REiNS International Collaboration series. Recommendations are based on expert panel consensus with limited prospective natural history data; no formal evidence grading methodology applied.</t>
-        </is>
-      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8124,17 +7904,9 @@
           <t>Clinical practice guideline</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>NF2-SWN</t>
-        </is>
-      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Hearing loss / Deafness; Facial weakness</t>
-        </is>
-      </c>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="3" t="inlineStr">
@@ -8354,65 +8126,29 @@
           <t>PMC XML</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Expert recommendation</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Vascular disease / anomaly</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N136" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O136" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P136" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>Weak/Conditional</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>Royal Victoria Infirmary – Newcastle Hospitals NHS Foundation Trust; Manchester Centre of Genomic Medicine</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>Retrospective single/dual-centre cohort study (n=27) with an explicit screening recommendation: routine biochemical screening (plasma free or urinary fractionated metanephrines) for PHEO/PG in all NF1 patients starting age 10–14 years, repeated every 3 years. Classified as 'expert recommendation' because the recommendation is author-derived from low-quality retrospective evidence rather than a formal guideline development process. PHEO/PG is not listed in the nf1_manifestations controlled vocabulary; vascular disease/anomaly is the closest available term. Borderline between 'Not a guideline' and 'Expert recommendation' — the explicit, structured recommendation with rationale justifies inclusion.</t>
-        </is>
-      </c>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12914,65 +12650,29 @@
           <t>abstract_only</t>
         </is>
       </c>
-      <c r="F222" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Consensus statement</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>NF1; NF2-SWN</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>Neuropathy</t>
-        </is>
-      </c>
+      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
-      <c r="M222" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N222" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O222" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P222" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>Diagnostic test appraisal; Consensus conference / expert panel</t>
-        </is>
-      </c>
-      <c r="R222" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr"/>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>Primary study validating handheld dynamometry (HHD) as an outcome measure for clinical trials, with reliability data from 33 NF1/NF2 patients. Concludes with consensus recommendations for HHD use in NF clinical trials. Borderline classification — it is primarily a reliability/validation study but explicitly provides consensus recommendations for trial methodology.</t>
-        </is>
-      </c>
+      <c r="T222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13374,69 +13074,29 @@
           <t>abstract_only</t>
         </is>
       </c>
-      <c r="F228" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Evidence-based recommendation</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>NF2-SWN</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>Hearing loss / Deafness</t>
-        </is>
-      </c>
+      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
-      <c r="M228" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N228" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O228" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P228" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>Systematic review &amp; meta-analysis; Patient/public &amp; qualitative methods</t>
-        </is>
-      </c>
-      <c r="R228" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>REiNS</t>
-        </is>
-      </c>
-      <c r="T228" t="inlineStr">
-        <is>
-          <t>REiNS Patient-Reported Outcomes Working Group recommendation for clinical trial endpoints; focuses on outcome measure selection (patient-reported hearing function and QoL) rather than direct clinical management or treatment. Systematic evaluation of published PRO measures with scoring and comparison on psychometric properties and feasibility.</t>
-        </is>
-      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15126,61 +14786,29 @@
           <t>PMC XML</t>
         </is>
       </c>
-      <c r="F260" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Expert recommendation</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
-      <c r="M260" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N260" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O260" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P260" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q260" t="inlineStr">
-        <is>
-          <t>Delphi method (modified); Consensus conference / expert panel</t>
-        </is>
-      </c>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>Expert opinion only</t>
-        </is>
-      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr"/>
-      <c r="T260" t="inlineStr">
-        <is>
-          <t>Focuses on the under-recognised skeletal muscle/myopathy phenotype in NF1 (muscle weakness, fatigue, motor deficits). Clinical recommendations are derived from a modified Delphi consensus within a single UK multidisciplinary NF1 service. Evidence base is limited to small clinical studies (max n=30); no formal guideline methodology (e.g. GRADE) applied. Covers assessment tools (dynamometry, 6-min walk, pGALS), investigations to exclude alternative causes, and management strategies including physiotherapy, occupational therapy, pacing, and emerging therapies (carnitine supplementation, whole-body vibration). Not affiliated with a named professional organisation.</t>
-        </is>
-      </c>
+      <c r="T260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -17158,14 +16786,14 @@
           <t>abstract_only</t>
         </is>
       </c>
-      <c r="F296" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Clinical practice guideline</t>
+          <t>Not a guideline or recommendation</t>
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
@@ -17173,46 +16801,14 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
-      <c r="M296" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N296" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O296" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P296" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q296" t="inlineStr">
-        <is>
-          <t>Consensus conference / expert panel</t>
-        </is>
-      </c>
-      <c r="R296" t="inlineStr">
-        <is>
-          <t>Not assessable</t>
-        </is>
-      </c>
-      <c r="S296" t="inlineStr">
-        <is>
-          <t>German dermatology society (AWMF S2k)</t>
-        </is>
-      </c>
-      <c r="T296" t="inlineStr">
-        <is>
-          <t>German S2k-level guideline on laser and optical radiation therapy for skin conditions. Mentions neurofibroma as one of many benign non-pigmented neoplasms treatable by laser, and café-au-lait spots (a hallmark of NF1) in the context of pigmented lesion treatment. However, the guideline is not focused on NF1 or any NF condition — these are incidental mentions within a broad dermatology laser guideline. No NF-specific conditions are the primary subject matter. Not relevant to the CTF NF guidelines.</t>
-        </is>
-      </c>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
+      <c r="S296" t="inlineStr"/>
+      <c r="T296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -18670,81 +18266,29 @@
           <t>PMC XML</t>
         </is>
       </c>
-      <c r="F324" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Expert recommendation</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>NF1; NF2-SWN; LZTR1-SWN; SMARCB1-SWN</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>Plexiform neurofibroma; Atypical neurofibroma; ANNUBP; MPNST / triton tumor; Cutaneous neurofibroma; Optic pathway glioma; Scoliosis; Vascular disease / anomaly</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Meningioma; Peripheral schwannoma; Paraspinal schwannoma; Ependymoma; Hearing loss / Deafness; Facial weakness; Neuropathy</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>Peripheral schwannoma; Paraspinal schwannoma</t>
-        </is>
-      </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>Peripheral schwannoma; Paraspinal schwannoma; Meningioma</t>
-        </is>
-      </c>
-      <c r="M324" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N324" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O324" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P324" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t>Consensus conference / expert panel</t>
-        </is>
-      </c>
-      <c r="R324" t="inlineStr">
-        <is>
-          <t>Weak/Conditional</t>
-        </is>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>EURACAN</t>
-        </is>
-      </c>
-      <c r="T324" t="inlineStr">
-        <is>
-          <t>Multidisciplinary EURACAN task force covering full spectrum of peripheral and cranial nerve sheath tumors (schwannoma, neurofibroma, PN, ANNUBP, MPNST, MMNST, perineurioma, HNST, cauda equina neuroendocrine tumor). Evidence classified per EFNS guidelines (Classes I–IV, Levels A–C); authors explicitly note very low evidence due to rarity of these tumors. Recommendations cover diagnosis (pathology, molecular, imaging), surgery, radiotherapy, and systemic therapy including selumetinib for NF1 plexiform neurofibromas. Literature reviewed through September 2022.</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr"/>
+      <c r="R324" t="inlineStr"/>
+      <c r="S324" t="inlineStr"/>
+      <c r="T324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18882,17 +18426,9 @@
           <t>Consensus statement</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>NF2-SWN; SMARCB1-SWN</t>
-        </is>
-      </c>
+      <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Meningioma; Peripheral schwannoma</t>
-        </is>
-      </c>
+      <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
       <c r="M327" s="3" t="inlineStr">
@@ -19744,69 +19280,29 @@
           <t>abstract_only</t>
         </is>
       </c>
-      <c r="F343" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Evidence-based recommendation</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>Plexiform neurofibroma</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
-      <c r="M343" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N343" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O343" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P343" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q343" t="inlineStr">
-        <is>
-          <t>GRADE (Evidence-to-Decision)</t>
-        </is>
-      </c>
-      <c r="R343" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="S343" t="inlineStr">
-        <is>
-          <t>CADTH</t>
-        </is>
-      </c>
-      <c r="T343" t="inlineStr">
-        <is>
-          <t>This is a Canadian Health Technology Assessment (HTA) reimbursement recommendation by CADTH for selumetinib (Koselugo) in pediatric NF1 patients (ages 2-18) with symptomatic, inoperable plexiform neurofibromas. Conditional reimbursement subject to price reduction and response criteria after 18 months. Based on SPRINT trial evidence.</t>
-        </is>
-      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr"/>
+      <c r="P343" t="inlineStr"/>
+      <c r="Q343" t="inlineStr"/>
+      <c r="R343" t="inlineStr"/>
+      <c r="S343" t="inlineStr"/>
+      <c r="T343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -20196,22 +19692,10 @@
           <t>Clinical practice guideline</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>NF2-SWN; LZTR1-SWN</t>
-        </is>
-      </c>
+      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Meningioma; Peripheral schwannoma; Hearing loss / Deafness; Facial weakness</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>Intracranial schwannoma</t>
-        </is>
-      </c>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr">
         <is>
@@ -21170,69 +20654,29 @@
           <t>PMC XML</t>
         </is>
       </c>
-      <c r="F368" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Evidence-based recommendation</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>Cutaneous neurofibroma; Plexiform neurofibroma</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr"/>
-      <c r="M368" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N368" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O368" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P368" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q368" t="inlineStr">
-        <is>
-          <t>Systematic review &amp; meta-analysis; Consensus conference / expert panel; Patient/public &amp; qualitative methods</t>
-        </is>
-      </c>
-      <c r="R368" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t>CTF (REiNS International Collaboration)</t>
-        </is>
-      </c>
-      <c r="T368" t="inlineStr">
-        <is>
-          <t>This is a REiNS PRO working group recommendation for use of the FACE-Q Craniofacial Module Appearance Distress scale as a patient-reported outcome measure in NF1 clinical trials targeting plexiform and cutaneous neurofibromas. The recommendation is based on a systematic review of 11 candidate PRO measures using the updated PRO Rating and Acceptance Tool for Endpoints (PRATE), with patient representative involvement. Focus is on clinical trial endpoint methodology rather than diagnosis, treatment, or surveillance per se. No GRADE framework was applied, but the process was systematic and consensus-based.</t>
-        </is>
-      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr"/>
+      <c r="R368" t="inlineStr"/>
+      <c r="S368" t="inlineStr"/>
+      <c r="T368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -21320,16 +20764,8 @@
           <t>Consensus statement</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>Optic pathway glioma; Low grade glioma</t>
-        </is>
-      </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr"/>
@@ -21460,17 +20896,9 @@
           <t>Expert recommendation</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>NF2-SWN</t>
-        </is>
-      </c>
+      <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Hearing loss / Deafness</t>
-        </is>
-      </c>
+      <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr"/>
       <c r="M372" s="2" t="inlineStr">
@@ -21636,69 +21064,29 @@
           <t>PMC XML</t>
         </is>
       </c>
-      <c r="F375" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Evidence-based recommendation</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>NF2-SWN</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
-      <c r="J375" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Hearing loss / Deafness</t>
-        </is>
-      </c>
+      <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr"/>
-      <c r="M375" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N375" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O375" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P375" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q375" t="inlineStr">
-        <is>
-          <t>Systematic review &amp; meta-analysis; Consensus conference / expert panel; Patient/public &amp; qualitative methods</t>
-        </is>
-      </c>
-      <c r="R375" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="S375" t="inlineStr">
-        <is>
-          <t>REiNS International Collaboration</t>
-        </is>
-      </c>
-      <c r="T375" t="inlineStr">
-        <is>
-          <t>REiNS PRO Communication Subgroup recommendation for use of the Tinnitus Functional Index as the preferred PROM for tinnitus assessment in NF2-SWN clinical trials. Based on systematic literature search, structured scoring via PRO-RATE tool, and expert/patient representative consensus; not a formal clinical practice guideline but a structured evidence-based recommendation for outcome measure selection in clinical trials.</t>
-        </is>
-      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+      <c r="O375" t="inlineStr"/>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr"/>
+      <c r="R375" t="inlineStr"/>
+      <c r="S375" t="inlineStr"/>
+      <c r="T375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -22322,31 +21710,11 @@
           <t>Consensus statement</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>NF1; NF2-SWN; LZTR1-SWN; SMARCB1-SWN</t>
-        </is>
-      </c>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>Optic pathway glioma; Low grade glioma; High grade glioma; MPNST / triton tumor</t>
-        </is>
-      </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>Meningioma; Peripheral schwannoma; Ependymoma</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>Peripheral schwannoma; Intracranial schwannoma</t>
-        </is>
-      </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>Peripheral schwannoma; Meningioma</t>
-        </is>
-      </c>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
       <c r="M387" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -23274,21 +22642,9 @@
           <t>Consensus statement</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>NF1; NF2-SWN</t>
-        </is>
-      </c>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>MPNST / triton tumor; Plexiform neurofibroma</t>
-        </is>
-      </c>
-      <c r="J405" t="inlineStr">
-        <is>
-          <t>Peripheral schwannoma</t>
-        </is>
-      </c>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr"/>
       <c r="M405" s="3" t="inlineStr">
@@ -23748,17 +23104,9 @@
           <t>Expert recommendation</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>NF2-SWN</t>
-        </is>
-      </c>
+      <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr"/>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>Vestibular schwannoma; Meningioma</t>
-        </is>
-      </c>
+      <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr"/>
       <c r="M412" s="2" t="inlineStr">
@@ -25190,69 +24538,29 @@
           <t>abstract_only</t>
         </is>
       </c>
-      <c r="F438" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Consensus statement</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>Plexiform neurofibroma; MPNST / triton tumor</t>
-        </is>
-      </c>
+          <t>Not a guideline or recommendation</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr"/>
-      <c r="M438" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N438" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O438" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P438" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q438" t="inlineStr">
-        <is>
-          <t>Consensus conference / expert panel</t>
-        </is>
-      </c>
-      <c r="R438" t="inlineStr">
-        <is>
-          <t>Expert opinion only</t>
-        </is>
-      </c>
-      <c r="S438" t="inlineStr">
-        <is>
-          <t>Plastic and Reconstructive Surgery Society of Chinese Medical Association (Group of Neurofibromatosis)</t>
-        </is>
-      </c>
-      <c r="T438" t="inlineStr">
-        <is>
-          <t>Chinese multidisciplinary expert consensus covering full course management of plexiform neurofibroma in NF1, including 18 recommendations on diagnosis, screening, surgical treatment, pharmacological treatment, disease monitoring, patient education, and psychological support. Published 2025. Evidence base described as existing evidence-based medicine evidence but methodology is primarily expert panel consensus. Includes MEK inhibitor (selumetinib) pharmacological treatment guidance.</t>
-        </is>
-      </c>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr"/>
+      <c r="O438" t="inlineStr"/>
+      <c r="P438" t="inlineStr"/>
+      <c r="Q438" t="inlineStr"/>
+      <c r="R438" t="inlineStr"/>
+      <c r="S438" t="inlineStr"/>
+      <c r="T438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -30020,16 +29328,8 @@
           <t>Consensus statement</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>NF1</t>
-        </is>
-      </c>
-      <c r="I528" t="inlineStr">
-        <is>
-          <t>Optic pathway glioma; Low grade glioma; Vascular disease / anomaly; Cognitive</t>
-        </is>
-      </c>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr"/>
@@ -30844,7 +30144,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C3" t="inlineStr"/>
     </row>
@@ -30865,7 +30165,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -30876,7 +30176,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C7" t="inlineStr"/>
     </row>
@@ -30887,7 +30187,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr"/>
     </row>
@@ -30898,7 +30198,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -30930,7 +30230,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C13" t="inlineStr"/>
     </row>
@@ -30941,7 +30241,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
@@ -30952,7 +30252,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -30963,7 +30263,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -30984,7 +30284,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C19" t="inlineStr"/>
     </row>
@@ -30995,7 +30295,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C20" t="inlineStr"/>
     </row>
@@ -31006,7 +30306,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C21" t="inlineStr"/>
     </row>
@@ -31017,7 +30317,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" t="inlineStr"/>
     </row>
@@ -31038,7 +30338,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C25" t="inlineStr"/>
     </row>
@@ -31060,7 +30360,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" t="inlineStr"/>
     </row>
@@ -31071,7 +30371,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C28" t="inlineStr"/>
     </row>
@@ -31082,7 +30382,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C29" t="inlineStr"/>
     </row>
@@ -31104,7 +30404,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C31" t="inlineStr"/>
     </row>
@@ -31115,7 +30415,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" t="inlineStr"/>
     </row>
@@ -31126,7 +30426,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" t="inlineStr"/>
     </row>
@@ -31137,7 +30437,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C34" t="inlineStr"/>
     </row>
@@ -31148,7 +30448,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" t="inlineStr"/>
     </row>
@@ -31170,7 +30470,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr"/>
     </row>
@@ -31181,7 +30481,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="inlineStr"/>
     </row>
@@ -31224,7 +30524,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C43" t="inlineStr"/>
     </row>
@@ -31235,7 +30535,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C44" t="inlineStr"/>
     </row>
@@ -31246,7 +30546,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C45" t="inlineStr"/>
     </row>
@@ -31257,7 +30557,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr"/>
     </row>
@@ -31268,7 +30568,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C47" t="inlineStr"/>
     </row>
@@ -31279,7 +30579,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C48" t="inlineStr"/>
     </row>
@@ -31290,7 +30590,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C49" t="inlineStr"/>
     </row>
@@ -31301,7 +30601,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C50" t="inlineStr"/>
     </row>
@@ -31333,7 +30633,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr"/>
     </row>
@@ -31344,7 +30644,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C55" t="inlineStr"/>
     </row>
@@ -31355,7 +30655,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" t="inlineStr"/>
     </row>
@@ -31387,7 +30687,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C60" t="inlineStr"/>
     </row>
@@ -31398,7 +30698,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61" t="inlineStr"/>
     </row>
@@ -31409,7 +30709,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr"/>
     </row>
@@ -31430,7 +30730,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C65" t="inlineStr"/>
     </row>
@@ -31441,7 +30741,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr"/>
     </row>
@@ -31452,7 +30752,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67" t="inlineStr"/>
     </row>
@@ -31474,7 +30774,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C69" t="inlineStr"/>
     </row>
@@ -31507,7 +30807,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C72" t="inlineStr"/>
     </row>
@@ -31540,7 +30840,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C75" t="inlineStr"/>
     </row>
@@ -31572,7 +30872,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C79" t="inlineStr"/>
     </row>
@@ -31583,7 +30883,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C80" t="inlineStr"/>
     </row>
@@ -31594,7 +30894,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C81" t="inlineStr"/>
     </row>
@@ -31605,7 +30905,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" t="inlineStr"/>
     </row>
@@ -31688,7 +30988,7 @@
         <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -31701,7 +31001,7 @@
         <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -31727,7 +31027,7 @@
         <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -31740,7 +31040,7 @@
         <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -31753,7 +31053,7 @@
         <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -31766,7 +31066,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -31779,7 +31079,7 @@
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">

--- a/NF_Guidelines_Curated.xlsx
+++ b/NF_Guidelines_Curated.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Classified Papers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary Counts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="By Year" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classified Papers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary Counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Year" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.5858/arpa.2015-0314-RA</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00381-016-3093-3</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:http://nrs.harvard.edu/urn-3:HUL.InstRepos:32725810</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://www.ncbi.nlm.nih.gov/pmc/articles/5578356</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://www.ncbi.nlm.nih.gov/pmc/articles/5578359</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:http://nrs.harvard.edu/urn-3:HUL.InstRepos:32725809</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:http://dspace.library.uu.nl/handle/1874/363421</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://research.manchester.ac.uk/en/publications/3229ea40-51a2-4efb-bd8b-b65ca0442ef1</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1055/s-0037-1608814</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1055/s-0037-1608869</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.5152/iao.2018.5348</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00381-018-3833-7</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PDF:Suerink Wimmer 2018 CMMRD as diff of NF1.pdf</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11547-018-0955-7</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PDF:e46.pdf</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1055/s-0039-1691830</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s10143-019-01135-y</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11060-019-03234-8</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11060-019-03247-3</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00256-019-03290-1</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://research.manchester.ac.uk/en/publications/216f3071-4682-4a6a-be22-d423c3fbcf75</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00405-019-05741-w</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1055/s-0040-1710524</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s12020-020-02351-z</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PDF:Journal of Genetic Counseling - 2020 - Radtke - Genetic Counseling for Neurofibromatosis 1 Neurofibromatosis 2 and.pdf</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00381-020-04706-3</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s12328-020-01227-z</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://www.ncbi.nlm.nih.gov/pmc/articles/7486535</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:http://hdl.handle.net/10072/416369</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://www.ncbi.nlm.nih.gov/pmc/articles/8246828</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PDF:Aronson 2021 Diagnostic criteria for CMMRD international consensus group.pdf</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00105-021-04779-4</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11906-021-01136-7</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00117-021-00861-z</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://www.ncbi.nlm.nih.gov/pmc/articles/8594008</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://www.ncbi.nlm.nih.gov/pmc/articles/8594001</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://www.ncbi.nlm.nih.gov/pmc/articles/8594004</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://pure.eur.nl/en/publications/8118ce3b-c70d-4b0b-b224-20b4e97efc4f</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00117-021-00892-6</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PMC XML</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s12070-020-02321-x</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:http://hdl.handle.net/10138/351298</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:http://hdl.handle.net/10072/426076</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://www.ncbi.nlm.nih.gov/pmc/articles/9018953</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11060-022-04104-6</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00117-022-01059-7</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11845-022-03184-7</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s12070-021-02900-6</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PDF:Halliday et al 2023 Updated protocol for genetic testing screening and clinical management of indiv at risk of NF2.SWN.pdf</t>
         </is>
       </c>
       <c r="F317" s="3" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00586-023-07600-z</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://hal.inrae.fr/hal-04246685/document</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1245/s10434-023-13519-y</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
@@ -18413,7 +18413,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PDF:Koza 2023 Consensus recommendations on counselling in Phelan-McDermid ring 22.pdf</t>
         </is>
       </c>
       <c r="F327" s="3" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s12070-022-03229-4</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s10689-023-00340-5</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://ojs.ptbioch.edu.pl/index.php/abp/article/download/6955/5839</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr">
@@ -19527,7 +19527,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PMC XML</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11912-023-01451-z</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
@@ -20201,7 +20201,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PMC XML</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00256-023-04511-4</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00586-023-08039-y</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
@@ -20501,7 +20501,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1055/s-0043-1777702</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PDF:https://discovery.ucl.ac.uk/10185874/2/Jacques_Consensus%20framework%20for%20conducting%20phase%20I_II%20clinical%20trials%20for%20children%2C%20adolescents%2C%20and%20young%20adults%20with%20pediatric%20low-grade%20glioma_AAM.pdf</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11136-023-03596-7</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s10143-024-02305-3</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
@@ -21347,7 +21347,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11060-024-04617-2</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00586-024-08194-w</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:http://urn.kb.se/resolve?urn=urn:nbn:se:uu:diva-577770</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
@@ -22479,7 +22479,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00330-024-10885-3</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
@@ -23395,7 +23395,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s10143-024-02889-w</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
@@ -24035,7 +24035,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s12070-024-04910-6</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
@@ -24385,7 +24385,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00431-024-05825-8</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>PDF:Dtsch_Arztebl_Int-122_071.pdf</t>
         </is>
       </c>
       <c r="F439" s="3" t="inlineStr">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00403-025-04056-7</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
@@ -25709,7 +25709,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://research.manchester.ac.uk/en/publications/0ee1dd1c-7856-4ae3-95ef-b487ee6a4ab4</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
@@ -25809,7 +25809,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s10143-025-03519-9</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
@@ -25909,7 +25909,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11033-025-10431-4</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -26409,7 +26409,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s10147-025-02793-3</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1038/s41434-025-00542-9</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
@@ -27289,7 +27289,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1038/s41416-025-03151-w</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00405-025-09734-w</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
@@ -27875,7 +27875,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11523-025-01176-y</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1038/s41388-025-03617-4</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s00431-025-06611-w</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
@@ -28965,7 +28965,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:doi:10.1007/s11060-025-05335-z</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
@@ -29215,7 +29215,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://doi.org/10.1038/s41431-026-02014-z</t>
         </is>
       </c>
       <c r="F526" s="2" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://cris.maastrichtuniversity.nl/en/publications/aeffa29c-94dc-4793-a566-de2d984aee9e</t>
         </is>
       </c>
       <c r="F529" s="2" t="inlineStr">
@@ -29697,7 +29697,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://pure.eur.nl/en/publications/9055de50-f17f-4d60-8149-6cd815b0c964</t>
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>abstract_only</t>
+          <t>HTML:https://doi.org/10.1186/s13256-026-06002-1</t>
         </is>
       </c>
       <c r="F539" s="2" t="inlineStr">
